--- a/analysis/課題0-1-2評価.xlsx
+++ b/analysis/課題0-1-2評価.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>量子アニーリング×メタサーフェスでROCF＋3手法。論文5本「全実在」と記すが2026年論文の検証は甘い疑い</t>
+          <t>量子アニーリング×メタサーフェスでROCF＋3手法。論文5本「全実在」と記すが本人提示のみでURL/DOI等の確認痕跡が薄い（4・5本目は2026年論文で実在し得るが要再確認）</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>階層型強化学習で4プロンプト構成（5本要件未達）。比較分析は丁寧だが、ハル検証で2026年の架空論文を「間違いなし」と誤認した可能性</t>
+          <t>階層型強化学習で4プロンプト構成（5本要件未達）。比較分析は丁寧だが、ハル検証で論文4-5本目が「ArXiv/2026年」のみで著者名・URLの確認が省略</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
